--- a/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/starter/data_retention_starter.xlsx
+++ b/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/starter/data_retention_starter.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +44,11 @@
       <i val="1"/>
       <color rgb="00888888"/>
     </font>
+    <font>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +81,12 @@
         <fgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +127,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -670,6 +682,27 @@
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Art. 7 — Consent records: controllers must demonstrate consent (Art. 7(1))</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Art. 5(1)(f) — Integrity and confidentiality of processing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Art. 12(3) — One-month default response window, extendable by 2 months for complex requests</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1092,47 +1125,47 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Which GDPR article?</t>
+          <t>[Your response here — name the GDPR Art. 6 basis covering AI-generated user queries (typically consent or legitimate interest); cross-reference rows 2-6 for the citation format.]</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — set a retention window for user query logs; weigh service-improvement value against minimization. Months-to-1-year is typical.]</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Where stored?</t>
+          <t>[Your response here — name the specific storage system (e.g., encrypted DB, S3 bucket, WORM log store, consent platform) that fits this data type.]</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — describe the access control model (RBAC, team-only, encrypted with key access, tamper-evident logs) appropriate to this data's sensitivity.]</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>[Your response here — Yes or No. For PHI and AI training data under HIPAA + GDPR Art. 32, encryption is generally required.]</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>How to delete?</t>
+          <t>[Your response here — name the deletion method (cryptographic erasure, NIST secure erase, batch purge, archival-only). Match the storage medium from column F.]</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>Any exceptions?</t>
+          <t>[Your response here — name any exceptions that extend retention (litigation hold, FDA inspection, active investigation, anonymization exemption).]</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Who owns?</t>
+          <t>[Your response here — name the accountable role (Privacy Officer, Compliance Officer, ML Operations Lead, Legal Department, Vendor Management).]</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>Review date</t>
+          <t>[Your response here — enter the last policy review date (YYYY-MM-DD); align with the cadence shown in pre-filled rows 2-6.]</t>
         </is>
       </c>
     </row>
@@ -1154,47 +1187,47 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Which GDPR article?</t>
+          <t>[Your response here — for CONSENT records, name the GDPR article that explicitly governs proof-of-consent (hint: Art. 7 referenced in the Scenario Brief).]</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — set a retention period long enough to prove consent during regulatory look-back windows (multi-year).]</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Where stored?</t>
+          <t>[Your response here — name the specific storage system (e.g., encrypted DB, S3 bucket, WORM log store, consent platform) that fits this data type.]</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — describe the access control model (RBAC, team-only, encrypted with key access, tamper-evident logs) appropriate to this data's sensitivity.]</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>[Your response here — Yes or No. For PHI and AI training data under HIPAA + GDPR Art. 32, encryption is generally required.]</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>How to delete?</t>
+          <t>[Your response here — name the deletion method (cryptographic erasure, NIST secure erase, batch purge, archival-only). Match the storage medium from column F.]</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>Any exceptions?</t>
+          <t>[Your response here — name any exceptions that extend retention (litigation hold, FDA inspection, active investigation, anonymization exemption).]</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Who owns?</t>
+          <t>[Your response here — name the accountable role (Privacy Officer, Compliance Officer, ML Operations Lead, Legal Department, Vendor Management).]</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>Review date</t>
+          <t>[Your response here — enter the last policy review date (YYYY-MM-DD); align with the cadence shown in pre-filled rows 2-6.]</t>
         </is>
       </c>
     </row>
@@ -1216,47 +1249,47 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Which GDPR article?</t>
+          <t>[Your response here — for AUDIT logs, name the GDPR article that establishes the legal-obligation basis for retention (look at row 6 for the same data type).]</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — set the audit-log retention period matching HIPAA/GDPR audit retention norms (see row 6 pattern).]</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Where stored?</t>
+          <t>[Your response here — name the specific storage system (e.g., encrypted DB, S3 bucket, WORM log store, consent platform) that fits this data type.]</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — describe the access control model (RBAC, team-only, encrypted with key access, tamper-evident logs) appropriate to this data's sensitivity.]</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>[Your response here — Yes or No. For PHI and AI training data under HIPAA + GDPR Art. 32, encryption is generally required.]</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>How to delete?</t>
+          <t>[Your response here — name the deletion method (cryptographic erasure, NIST secure erase, batch purge, archival-only). Match the storage medium from column F.]</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>Any exceptions?</t>
+          <t>[Your response here — name any exceptions that extend retention (litigation hold, FDA inspection, active investigation, anonymization exemption).]</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Who owns?</t>
+          <t>[Your response here — name the accountable role (Privacy Officer, Compliance Officer, ML Operations Lead, Legal Department, Vendor Management).]</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>Review date</t>
+          <t>[Your response here — enter the last policy review date (YYYY-MM-DD); align with the cadence shown in pre-filled rows 2-6.]</t>
         </is>
       </c>
     </row>
@@ -1278,47 +1311,47 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Which GDPR article?</t>
+          <t>[Your response here — for anonymized research data, note the GDPR scope rule (Recital 26) and pick the most defensible Art. 6 basis if anonymization is incomplete.]</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — set retention for properly anonymized research data; the GDPR exemption may allow extended or indefinite retention.]</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Where stored?</t>
+          <t>[Your response here — name the specific storage system (e.g., encrypted DB, S3 bucket, WORM log store, consent platform) that fits this data type.]</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — describe the access control model (RBAC, team-only, encrypted with key access, tamper-evident logs) appropriate to this data's sensitivity.]</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>[Your response here — Yes or No. For PHI and AI training data under HIPAA + GDPR Art. 32, encryption is generally required.]</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>How to delete?</t>
+          <t>[Your response here — name the deletion method (cryptographic erasure, NIST secure erase, batch purge, archival-only). Match the storage medium from column F.]</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>Any exceptions?</t>
+          <t>[Your response here — name any exceptions that extend retention (litigation hold, FDA inspection, active investigation, anonymization exemption).]</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Who owns?</t>
+          <t>[Your response here — name the accountable role (Privacy Officer, Compliance Officer, ML Operations Lead, Legal Department, Vendor Management).]</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>Review date</t>
+          <t>[Your response here — enter the last policy review date (YYYY-MM-DD); align with the cadence shown in pre-filled rows 2-6.]</t>
         </is>
       </c>
     </row>
@@ -1340,47 +1373,47 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Which GDPR article?</t>
+          <t>[Your response here — for vendor-shared data covered by a DPA, name the GDPR Art. 6 basis tied to contractual processing (see Scenario Brief Art. 28).]</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — tie retention to the contract / DPA duration plus a defensible buffer.]</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Where stored?</t>
+          <t>[Your response here — name the specific storage system (e.g., encrypted DB, S3 bucket, WORM log store, consent platform) that fits this data type.]</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — describe the access control model (RBAC, team-only, encrypted with key access, tamper-evident logs) appropriate to this data's sensitivity.]</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>[Your response here — Yes or No. For PHI and AI training data under HIPAA + GDPR Art. 32, encryption is generally required.]</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>How to delete?</t>
+          <t>[Your response here — name the deletion method (cryptographic erasure, NIST secure erase, batch purge, archival-only). Match the storage medium from column F.]</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>Any exceptions?</t>
+          <t>[Your response here — name any exceptions that extend retention (litigation hold, FDA inspection, active investigation, anonymization exemption).]</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Who owns?</t>
+          <t>[Your response here — name the accountable role (Privacy Officer, Compliance Officer, ML Operations Lead, Legal Department, Vendor Management).]</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>Review date</t>
+          <t>[Your response here — enter the last policy review date (YYYY-MM-DD); align with the cadence shown in pre-filled rows 2-6.]</t>
         </is>
       </c>
     </row>
@@ -1402,47 +1435,47 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Which GDPR article?</t>
+          <t>[Your response here — for model evaluation results, name the GDPR Art. 6 basis tied to improving processing operations (legitimate interest pattern).]</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — set retention covering at least one model-version cycle so evaluations remain comparable.]</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Where stored?</t>
+          <t>[Your response here — name the specific storage system (e.g., encrypted DB, S3 bucket, WORM log store, consent platform) that fits this data type.]</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — describe the access control model (RBAC, team-only, encrypted with key access, tamper-evident logs) appropriate to this data's sensitivity.]</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>[Your response here — Yes or No. For PHI and AI training data under HIPAA + GDPR Art. 32, encryption is generally required.]</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>How to delete?</t>
+          <t>[Your response here — name the deletion method (cryptographic erasure, NIST secure erase, batch purge, archival-only). Match the storage medium from column F.]</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Any exceptions?</t>
+          <t>[Your response here — name any exceptions that extend retention (litigation hold, FDA inspection, active investigation, anonymization exemption).]</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Who owns?</t>
+          <t>[Your response here — name the accountable role (Privacy Officer, Compliance Officer, ML Operations Lead, Legal Department, Vendor Management).]</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>Review date</t>
+          <t>[Your response here — enter the last policy review date (YYYY-MM-DD); align with the cadence shown in pre-filled rows 2-6.]</t>
         </is>
       </c>
     </row>
@@ -1464,47 +1497,47 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Which GDPR article?</t>
+          <t>[Your response here — for full system backups (mixed data), name the GDPR Art. 6 basis that justifies retention as a continuity obligation.]</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — set retention aligned with the backup rotation policy (think days-to-weeks for offsite rotation).]</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Where stored?</t>
+          <t>[Your response here — name the specific storage system (e.g., encrypted DB, S3 bucket, WORM log store, consent platform) that fits this data type.]</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — describe the access control model (RBAC, team-only, encrypted with key access, tamper-evident logs) appropriate to this data's sensitivity.]</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>[Your response here — Yes or No. For PHI and AI training data under HIPAA + GDPR Art. 32, encryption is generally required.]</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>How to delete?</t>
+          <t>[Your response here — name the deletion method (cryptographic erasure, NIST secure erase, batch purge, archival-only). Match the storage medium from column F.]</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>Any exceptions?</t>
+          <t>[Your response here — name any exceptions that extend retention (litigation hold, FDA inspection, active investigation, anonymization exemption).]</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Who owns?</t>
+          <t>[Your response here — name the accountable role (Privacy Officer, Compliance Officer, ML Operations Lead, Legal Department, Vendor Management).]</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>Review date</t>
+          <t>[Your response here — enter the last policy review date (YYYY-MM-DD); align with the cadence shown in pre-filled rows 2-6.]</t>
         </is>
       </c>
     </row>
@@ -1666,41 +1699,41 @@
     </row>
     <row r="4">
       <c r="A4" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Model Impact Assessment</t>
+          <t>[Your response here — name the stage that clarifies the SCOPE of the deletion request (full vs partial, which data categories are in/out).]</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Identify all AI models trained on deleted data; assess retraining needs</t>
+          <t>[Your response here — describe what this stage does in 1-2 sentences. Reference the Scenario Brief for HealthBridge-specific constraints.]</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>ML Engineering Manager</t>
+          <t>[Your response here — name the role accountable. Think: who owns scoping decisions vs identity verification (Step 2)?]</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>48 hours</t>
+          <t>[Your response here — set an SLA shorter than Step 2 if this is a clarification, or longer if it requires legal review.]</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>Cross-reference model lineage against deleted data types</t>
+          <t>[Your response here — what evidence shows the scope was correctly determined?]</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>CDO if HIGH priority retraining identified</t>
+          <t>[Your response here — who handles scope ambiguity (Privacy Team, Legal, Compliance Officer)?]</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>Impact assessment report + retraining timeline</t>
+          <t>[Your response here — what artifact is produced (scoping memo, classification ticket, etc.)?]</t>
         </is>
       </c>
     </row>
@@ -1710,37 +1743,37 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>What stage name?</t>
+          <t>[Your response here — name the stage that inventories WHICH systems hold this subject's data.]</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Describe the process</t>
+          <t>[Your response here — describe the search across systems (EHR, S3 training data, backups, inference logs). HealthBridge has many.]</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Which role?</t>
+          <t>[Your response here — name the role accountable. Think: who has visibility across data systems (Data Engineer, Data Governance Lead)?]</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — set an SLA that reflects the breadth of systems. The Scenario Brief lists 5+ data stores.]</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>What to validate?</t>
+          <t>[Your response here — how do you know you found every record (cross-referencing data_inventory, confirming completeness)?]</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Who to escalate to?</t>
+          <t>[Your response here — escalate to whom if a system is missing or inaccessible?]</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>What artifact?</t>
+          <t>[Your response here — what artifact is produced (data inventory report listing every record + storage location)?]</t>
         </is>
       </c>
     </row>
@@ -1750,37 +1783,37 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>What stage name?</t>
+          <t>Model Impact Assessment</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Describe the process</t>
+          <t>Identify all AI models trained on deleted data; assess retraining needs</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Which role?</t>
+          <t>ML Engineering Manager</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>48 hours</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>What to validate?</t>
+          <t>Cross-reference model lineage against deleted data types</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Who to escalate to?</t>
+          <t>CDO if HIGH priority retraining identified</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>What artifact?</t>
+          <t>Impact assessment report + retraining timeline</t>
         </is>
       </c>
     </row>
@@ -1790,37 +1823,37 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>What stage name?</t>
+          <t>[Your response here — name the stage that EXECUTES the actual deletion across all systems.]</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Describe the process</t>
+          <t>[Your response here — describe the multi-system deletion (primary DB, backups, archives). The longest step in the workflow.]</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Which role?</t>
+          <t>[Your response here — name the role accountable. Likely Engineering / DevOps with approval from a senior role.]</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — this is the longest step. Set an SLA in days that reflects backup-rotation timing.]</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>What to validate?</t>
+          <t>[Your response here — how do you confirm deletion succeeded across ALL systems including offsite backups?]</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Who to escalate to?</t>
+          <t>[Your response here — who approves deletion sign-off (CTO, CISO)?]</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>What artifact?</t>
+          <t>[Your response here — what artifact records the deletion (deletion certificate per system, hash log)?]</t>
         </is>
       </c>
     </row>
@@ -1830,37 +1863,37 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>What stage name?</t>
+          <t>[Your response here — name the stage that VERIFIES the deletion was complete (independent of the engineer who ran it).]</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Describe the process</t>
+          <t>[Your response here — describe the independent verification (sample-based check, backup-restoration test, hash diff).]</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Which role?</t>
+          <t>[Your response here — separation-of-duties matters here. Who is NOT the executor but can audit?]</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — set an SLA that allows thorough auditing but not so long it delays compliance reporting.]</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>What to validate?</t>
+          <t>[Your response here — what is the gold-standard verification (e.g., restore a backup, confirm no record)?]</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Who to escalate to?</t>
+          <t>[Your response here — who handles verification failures (Compliance Officer, DPO)?]</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>What artifact?</t>
+          <t>[Your response here — what artifact (verification report signed by an independent auditor)?]</t>
         </is>
       </c>
     </row>
@@ -1870,37 +1903,37 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>What stage name?</t>
+          <t>[Your response here — name the stage that NOTIFIES the data subject the deletion is complete.]</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Describe the process</t>
+          <t>[Your response here — describe the notification (channel, content, proof-of-delivery). GDPR Art. 12(3) requires this.]</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Which role?</t>
+          <t>[Your response here — name the role that closes the loop with the subject (Privacy Team, Customer Success).]</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — quick SLA — the subject has been waiting throughout the workflow.]</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>What to validate?</t>
+          <t>[Your response here — proof the notification reached the subject (certified mail, email read receipt)?]</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Who to escalate to?</t>
+          <t>[Your response here — what happens if the subject can't be reached?]</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>What artifact?</t>
+          <t>[Your response here — what artifact (signed acknowledgement, delivery confirmation)?]</t>
         </is>
       </c>
     </row>
@@ -1910,37 +1943,37 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>What stage name?</t>
+          <t>[Your response here — name the stage that writes the IMMUTABLE audit log entry for this entire request.]</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Describe the process</t>
+          <t>[Your response here — describe what goes in the audit log (request ID, timeline, deletion methods, models retrained, sign-offs).]</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Which role?</t>
+          <t>[Your response here — name the role that owns the immutable audit log (DPO, Compliance Officer, Security).]</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — set an SLA — log should be written within a tight window of completion.]</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>What to validate?</t>
+          <t>[Your response here — how is the log made tamper-evident (hash chain, append-only store, signed)?]</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Who to escalate to?</t>
+          <t>[Your response here — who reviews the log for completeness (auditor, internal compliance)?]</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>What artifact?</t>
+          <t>[Your response here — what artifact (immutable audit log entry in the compliance repository)?]</t>
         </is>
       </c>
     </row>
@@ -1950,37 +1983,37 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>What stage name?</t>
+          <t>[Your response here — name the stage that NOTIFIES the supervisory authority IF required.]</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Describe the process</t>
+          <t>[Your response here — describe when DPA/regulator notification triggers (e.g., breach during deletion, jurisdictional rules).]</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Which role?</t>
+          <t>[Your response here — name the role that owns regulator-facing communications (DPO, Legal Counsel).]</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>How long?</t>
+          <t>[Your response here — GDPR Art. 12(3) default is one month, extendable by two further months for complex / numerous requests.]</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>What to validate?</t>
+          <t>[Your response here — how do you verify the regulator received and acknowledged?]</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Who to escalate to?</t>
+          <t>[Your response here — who handles non-acknowledgement from the regulator?]</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>What artifact?</t>
+          <t>[Your response here — what artifact (filed regulator notification, acknowledgement letter)?]</t>
         </is>
       </c>
     </row>
@@ -2088,27 +2121,27 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>What data to capture?</t>
+          <t>[Your response here — list 4-6 fields to capture for a GDPR Art. 17 deletion request (think: request ID, subject ID, timestamp, scope, approver, execution result).]</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>How long to retain?</t>
+          <t>[Your response here — set audit retention long enough to prove compliance during regulator look-back (multi-year). Use row 2 as benchmark.]</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>How to store?</t>
+          <t>[Your response here — name the immutable storage mechanism (e.g., WORM, append-only DB) that prevents tampering.]</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — name the roles allowed to read (Compliance team, Legal, DPO); follow row 2 pattern.]</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>Which regulation?</t>
+          <t>[Your response here — cite the GDPR article that mandates logging this event (hint: Right to Erasure is in Scenario Brief).]</t>
         </is>
       </c>
     </row>
@@ -2120,27 +2153,27 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>What data to capture?</t>
+          <t>[Your response here — list fields needed to reconstruct a change (e.g., user, timestamp, field, old/new value, reason).]</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>How long to retain?</t>
+          <t>[Your response here — set retention matching the integrity/audit baseline from row 2.]</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>How to store?</t>
+          <t>[Your response here — name a change-data-capture mechanism appropriate for tracking field-level edits.]</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — name the roles allowed to review modifications (Data Governance, Compliance).]</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>Which regulation?</t>
+          <t>[Your response here — cite the GDPR article on integrity &amp; confidentiality (referenced in Scenario Brief).]</t>
         </is>
       </c>
     </row>
@@ -2152,27 +2185,27 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>What data to capture?</t>
+          <t>[Your response here — list fields to log when consent is granted or withdrawn (subject ID, timestamp, consent type, action, method).]</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>How long to retain?</t>
+          <t>[Your response here — set retention long enough to prove consent state during disputes; tie to the consent-records retention in Retention Policy.]</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>How to store?</t>
+          <t>[Your response here — name the storage system housing consent audit records (consent platform audit table or similar).]</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — name the roles allowed to view consent history (Privacy team, Legal).]</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Which regulation?</t>
+          <t>[Your response here — cite the GDPR article that mandates consent records (hint: Art. 7 in Scenario Brief).]</t>
         </is>
       </c>
     </row>
@@ -2184,27 +2217,27 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>What data to capture?</t>
+          <t>[Your response here — list fields capturing IAM changes (admin ID, timestamp, user/role modified, permission delta, reason).]</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>How long to retain?</t>
+          <t>[Your response here — set retention matching the security audit baseline (typically multi-year, see row 2).]</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>How to store?</t>
+          <t>[Your response here — name the IAM/SIEM log store used for permission-change records.]</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — name the roles allowed to review permission changes (Security, Audit committee).]</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Which regulation?</t>
+          <t>[Your response here — cite the GDPR article covering security of processing &amp; access control (Scenario Brief).]</t>
         </is>
       </c>
     </row>
@@ -2216,27 +2249,27 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>What data to capture?</t>
+          <t>[Your response here — list fields linking a retraining run to the triggering data event (model ID, trigger type, training data version, completion timestamp, approver).]</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>How long to retain?</t>
+          <t>[Your response here — set retention spanning the model's operational life plus a buffer after retirement.]</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>How to store?</t>
+          <t>[Your response here — name the ML experiment-tracking system (e.g., MLflow, W&amp;B) that records retraining lineage.]</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — name the roles allowed to view retraining audits (ML team, Data Governance).]</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Which regulation?</t>
+          <t>[Your response here — cite the GDPR article requiring DPIAs for high-risk automated processing (Scenario Brief).]</t>
         </is>
       </c>
     </row>
@@ -2248,27 +2281,27 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>What data to capture?</t>
+          <t>[Your response here — list fields documenting a security or privacy incident (incident ID, timestamp, involved parties, actions taken, resolution, impact).]</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>How long to retain?</t>
+          <t>[Your response here — set retention covering investigation hold periods (often 7 years or per legal hold).]</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>How to store?</t>
+          <t>[Your response here — name a secure incident-management system with restricted access.]</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — name the roles allowed to access incident records (Security, Legal, Compliance).]</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Which regulation?</t>
+          <t>[Your response here — cite the GDPR article on breach notification (72-hour rule referenced in Scenario Brief).]</t>
         </is>
       </c>
     </row>
@@ -2280,27 +2313,27 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>What data to capture?</t>
+          <t>[Your response here — list fields documenting an outbound data transfer (vendor ID, timestamp, data type, volume, transfer method, approval, DPA reference).]</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>How long to retain?</t>
+          <t>[Your response here — tie retention to the vendor contract duration plus a defensible buffer.]</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>How to store?</t>
+          <t>[Your response here — name the DPA/vendor governance system holding transfer records.]</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Who can access?</t>
+          <t>[Your response here — name the roles allowed to view third-party transfer logs (Vendor Management, Legal).]</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Which regulation?</t>
+          <t>[Your response here — cite the GDPR article governing processor obligations (Scenario Brief Art. 28).]</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2464,40 +2497,129 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TR-003</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — name a Retention-Policy data type that, when deleted, would touch a HealthBridge model (e.g., Model Training Dataset, User Queries, Consent Records, Audit Logs).]</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — name the HealthBridge model(s) trained on or dependent on this data; cross-reference rows 2-3 for the naming pattern.]</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — rate impact (None / Low / Medium / High / Critical) based on how central this data is to the model.]</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — Yes or No. Tie to impact: archival-only or peripheral data may not need retraining.]</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — set a retraining timeline range in days, or 'N/A' if no retraining is required.]</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — name the approving role (ML Engineering Manager, VP of R&amp;D, Compliance Officer, Data Governance) appropriate to the impact tier.]</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — write a 1-line rationale explaining the impact rating and retraining decision (1-2 sentences).]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TR-004</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — name a Retention-Policy data type that, when deleted, would touch a HealthBridge model (e.g., Model Training Dataset, User Queries, Consent Records, Audit Logs).]</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — name the HealthBridge model(s) trained on or dependent on this data; cross-reference rows 2-3 for the naming pattern.]</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — rate impact (None / Low / Medium / High / Critical) based on how central this data is to the model.]</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — Yes or No. Tie to impact: archival-only or peripheral data may not need retraining.]</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — set a retraining timeline range in days, or 'N/A' if no retraining is required.]</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — name the approving role (ML Engineering Manager, VP of R&amp;D, Compliance Officer, Data Governance) appropriate to the impact tier.]</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — write a 1-line rationale explaining the impact rating and retraining decision (1-2 sentences).]</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TR-004</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>TR-005</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TR-006</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TR-007</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TR-008</t>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — name a Retention-Policy data type that, when deleted, would touch a HealthBridge model (e.g., Model Training Dataset, User Queries, Consent Records, Audit Logs).]</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — name the HealthBridge model(s) trained on or dependent on this data; cross-reference rows 2-3 for the naming pattern.]</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — rate impact (None / Low / Medium / High / Critical) based on how central this data is to the model.]</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — Yes or No. Tie to impact: archival-only or peripheral data may not need retraining.]</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — set a retraining timeline range in days, or 'N/A' if no retraining is required.]</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — name the approving role (ML Engineering Manager, VP of R&amp;D, Compliance Officer, Data Governance) appropriate to the impact tier.]</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>[Your response here — write a 1-line rationale explaining the impact rating and retraining decision (1-2 sentences).]</t>
         </is>
       </c>
     </row>

--- a/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/starter/data_retention_starter.xlsx
+++ b/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/starter/data_retention_starter.xlsx
@@ -607,7 +607,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>3. Document 8 retraining triggers mapping deleted data to affected models</t>
+          <t>3. Document the 5 retraining triggers mapping deleted data to affected models</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr"/>

--- a/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/starter/data_retention_starter.xlsx
+++ b/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/starter/data_retention_starter.xlsx
@@ -1254,7 +1254,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>[Your response here — set the audit-log retention period matching HIPAA/GDPR audit retention norms (see row 6 pattern).]</t>
+          <t>[Your response here — set the audit-log retention period noting HIPAA's 6-year Security-Rule documentation rule (GDPR sets no fixed audit-log period) (see row 6 pattern).]</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
